--- a/从零开始学Slots/从零开始学Slots-32-基础篇-MegaSymbols.xlsx
+++ b/从零开始学Slots/从零开始学Slots-32-基础篇-MegaSymbols.xlsx
@@ -8721,6 +8721,9 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <ignoredErrors>
+    <ignoredError sqref="A1:N160" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -9387,5 +9390,8 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <ignoredErrors>
+    <ignoredError sqref="A1:M76" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/从零开始学Slots/从零开始学Slots-32-基础篇-MegaSymbols.xlsx
+++ b/从零开始学Slots/从零开始学Slots-32-基础篇-MegaSymbols.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="217">
   <si>
     <r>
       <rPr>
@@ -7653,7 +7653,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="33">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -7780,6 +7780,10 @@
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -9009,8 +9013,8 @@
         <f aca="false">B23/3</f>
         <v>3</v>
       </c>
-      <c r="C25" s="15" t="s">
-        <v>158</v>
+      <c r="C25" s="32">
+        <v>9</v>
       </c>
       <c r="D25" s="15"/>
       <c r="E25" s="15"/>
